--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484559_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484559_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.8267</v>
+        <v>6.9857</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9312</v>
+        <v>5.3132</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8954</v>
+        <v>1.6725</v>
       </c>
       <c r="G2" t="n">
         <v>3.2972</v>
@@ -610,13 +610,13 @@
         <v>1.0995</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1055</v>
+        <v>1.2645</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9035</v>
+        <v>1.2855</v>
       </c>
       <c r="U2" t="n">
-        <v>0.202</v>
+        <v>-0.021</v>
       </c>
       <c r="V2" t="n">
         <v>3.157</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1663</v>
+        <v>6.3608</v>
       </c>
       <c r="E3" t="n">
-        <v>2.464</v>
+        <v>3.0548</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7024</v>
+        <v>3.306</v>
       </c>
       <c r="G3" t="n">
         <v>4.7247</v>
@@ -688,13 +688,13 @@
         <v>1.6493</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7086</v>
+        <v>0.9031</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8258</v>
+        <v>-0.2349</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5344</v>
+        <v>1.138</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. MORTE MONTANES</t>
+          <t>M. MORAGAS AZNAR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.1175</v>
+        <v>5.3534</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0392</v>
+        <v>3.0655</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0783</v>
+        <v>2.2879</v>
       </c>
       <c r="G4" t="n">
-        <v>0.92</v>
+        <v>0.6572</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8177</v>
+        <v>1.3045</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.8976</v>
+        <v>-0.6474</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3982</v>
+        <v>1.2054</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7122</v>
+        <v>1.6282</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.3141</v>
+        <v>-0.4228</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4781</v>
+        <v>-0.5483</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8946</v>
+        <v>-0.3237</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4164</v>
+        <v>-0.2246</v>
       </c>
       <c r="P4" t="n">
-        <v>0.733</v>
+        <v>1.6493</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R4" t="n">
         <v>2.5656</v>
       </c>
       <c r="S4" t="n">
-        <v>2.8755</v>
+        <v>0.513</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8846</v>
+        <v>-0.0795</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9908</v>
+        <v>0.5926</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5889</v>
+        <v>2.5339</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5889</v>
+        <v>2.8559</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. MORAGAS AZNAR</t>
+          <t>A. CEJUDO GALAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.4688</v>
+        <v>5.2172</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1066</v>
+        <v>1.5206</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3623</v>
+        <v>3.6966</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6572</v>
+        <v>2.5049</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3045</v>
+        <v>2.2196</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6474</v>
+        <v>0.2854</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2054</v>
+        <v>1.6413</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6282</v>
+        <v>1.5481</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.4228</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5483</v>
+        <v>0.8637</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3237</v>
+        <v>0.6715</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2246</v>
+        <v>0.1922</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6493</v>
+        <v>2.1991</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5656</v>
+        <v>2.1991</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6284</v>
+        <v>0.5132</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0384</v>
+        <v>-0.1206</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6669</v>
+        <v>0.6338</v>
       </c>
       <c r="V5" t="n">
-        <v>2.5339</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.8559</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. CEJUDO GALAN</t>
+          <t>P. MORTE MONTANES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.6348</v>
+        <v>4.7953</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8885999999999999</v>
+        <v>2.1877</v>
       </c>
       <c r="F6" t="n">
-        <v>3.7461</v>
+        <v>2.6076</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5049</v>
+        <v>0.92</v>
       </c>
       <c r="H6" t="n">
-        <v>2.2196</v>
+        <v>2.8177</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2854</v>
+        <v>-1.8976</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6413</v>
+        <v>1.3982</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5481</v>
+        <v>3.7122</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09320000000000001</v>
+        <v>-2.3141</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8637</v>
+        <v>-0.4781</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6715</v>
+        <v>-0.8946</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1922</v>
+        <v>0.4164</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1991</v>
+        <v>0.733</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1991</v>
+        <v>2.5656</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0692</v>
+        <v>1.5533</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7526</v>
+        <v>1.0332</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6834</v>
+        <v>0.5201</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.5889</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.5889</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. VILLAR SOLER</t>
+          <t>M. GARRIDO TALENS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.7946</v>
+        <v>3.021</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2578</v>
+        <v>3.8576</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0524</v>
+        <v>-0.8366</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2958</v>
+        <v>4.3616</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2799</v>
+        <v>1.342</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0159</v>
+        <v>3.0196</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1643</v>
+        <v>4.5495</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3002</v>
+        <v>1.8824</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.4645</v>
+        <v>2.6672</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1315</v>
+        <v>-0.1879</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.5404</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4486</v>
+        <v>0.3525</v>
       </c>
       <c r="P7" t="n">
-        <v>1.2828</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1991</v>
+        <v>0.9163</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1845</v>
+        <v>0.5311</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8228</v>
+        <v>0.5072</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3618</v>
+        <v>0.0239</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6231</v>
+        <v>-0.9554</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.6335</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6231</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. GARRIDO TALENS</t>
+          <t>J. VILLAR SOLER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.3554</v>
+        <v>2.6498</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5141</v>
+        <v>-0.7246</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1587</v>
+        <v>3.3744</v>
       </c>
       <c r="G8" t="n">
-        <v>4.3616</v>
+        <v>-0.2958</v>
       </c>
       <c r="H8" t="n">
-        <v>1.342</v>
+        <v>-0.2799</v>
       </c>
       <c r="I8" t="n">
-        <v>3.0196</v>
+        <v>-0.0159</v>
       </c>
       <c r="J8" t="n">
-        <v>4.5495</v>
+        <v>-0.1643</v>
       </c>
       <c r="K8" t="n">
-        <v>1.8824</v>
+        <v>0.3002</v>
       </c>
       <c r="L8" t="n">
-        <v>2.6672</v>
+        <v>-0.4645</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1879</v>
+        <v>-0.1315</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5404</v>
+        <v>-0.5800999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3525</v>
+        <v>0.4486</v>
       </c>
       <c r="P8" t="n">
+        <v>1.2828</v>
+      </c>
+      <c r="Q8" t="n">
         <v>-0.9163</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-1.8326</v>
-      </c>
       <c r="R8" t="n">
-        <v>0.9163</v>
+        <v>2.1991</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1345</v>
+        <v>1.0398</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1637</v>
+        <v>0.356</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2981</v>
+        <v>0.6838</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9554</v>
+        <v>0.6231</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6335</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.5889</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="9">
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. MORTE MONTAÑES</t>
+          <t>A. PEREZ RIPOLL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6251</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6251</v>
+        <v>1.1</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-0.157</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6251</v>
+        <v>2.0341</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.5723</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6251</v>
+        <v>1.4618</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6251</v>
+        <v>1.2436</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.5511</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6251</v>
+        <v>0.6925</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>0.7905</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>0.0213</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.7692</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.1833</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.0995</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>0.6365</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>0.7726</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0.1361</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.9109</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.9109</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. PEREZ RIPOLL</t>
+          <t>P. MORTE MONTAÑES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4127</v>
+        <v>0.6251</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6192</v>
+        <v>0.6251</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2065</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2.0341</v>
+        <v>0.6251</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5723</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4618</v>
+        <v>0.6251</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2436</v>
+        <v>0.6251</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5511</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6925</v>
+        <v>0.6251</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7905</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0213</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7692</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1833</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.0995</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1062</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2919</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1857</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.9109</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.9109</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.2053</v>
+        <v>-0.7712</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6111</v>
+        <v>-0.2264</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5943000000000001</v>
+        <v>-0.5447</v>
       </c>
       <c r="G12" t="n">
         <v>-0.8537</v>
@@ -1390,13 +1390,13 @@
         <v>0.1833</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5348000000000001</v>
+        <v>-0.1007</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0551</v>
+        <v>0.3296</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4798</v>
+        <v>-0.4302</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. MARIA VENTURA</t>
+          <t>G. VOLPATO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.8284</v>
+        <v>-2.899</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.9197</v>
+        <v>-3.3495</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9087</v>
+        <v>0.4505</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.0733</v>
+        <v>-3.9938</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.7079</v>
+        <v>0.4963</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.3654</v>
+        <v>-4.4901</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.6317</v>
+        <v>-4.5033</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.4587</v>
+        <v>-0.0775</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.1729</v>
+        <v>-4.4258</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5584</v>
+        <v>0.5095</v>
       </c>
       <c r="N13" t="n">
-        <v>0.7508</v>
+        <v>0.5738</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1925</v>
+        <v>-0.0643</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9163</v>
+        <v>1.0995</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9163</v>
+        <v>1.0995</v>
       </c>
       <c r="S13" t="n">
-        <v>1.7501</v>
+        <v>-0.0047</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5445</v>
+        <v>0.5204</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7944</v>
+        <v>-0.5251</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.5889</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.6335</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.5889</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. VOLPATO</t>
+          <t>M. MARIA VENTURA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.369</v>
+        <v>-3.7316</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.6956</v>
+        <v>-3.1697</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3266</v>
+        <v>-0.5619</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.9938</v>
+        <v>-2.0733</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4963</v>
+        <v>-0.7079</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.4901</v>
+        <v>-1.3654</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.5033</v>
+        <v>-2.6317</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.0775</v>
+        <v>-1.4587</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.4258</v>
+        <v>-1.1729</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5095</v>
+        <v>0.5584</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5738</v>
+        <v>0.7508</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0643</v>
+        <v>-0.1925</v>
       </c>
       <c r="P14" t="n">
-        <v>1.0995</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R14" t="n">
-        <v>1.0995</v>
+        <v>0.9163</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.4747</v>
+        <v>0.8469</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8258</v>
+        <v>1.2945</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.649</v>
+        <v>-0.4476</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-1.5889</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6335</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6335</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="15">
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>29.2494</v>
+        <v>29.79969999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>13.954</v>
+        <v>14.5045</v>
       </c>
       <c r="F15" t="n">
         <v>15.2953</v>
@@ -1594,7 +1594,7 @@
         <v>12.5159</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6424999999999992</v>
+        <v>0.6424999999999994</v>
       </c>
       <c r="J15" t="n">
         <v>11.2684</v>
@@ -1603,7 +1603,7 @@
         <v>12.5476</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.279100000000001</v>
+        <v>-1.2791</v>
       </c>
       <c r="M15" t="n">
         <v>1.8901</v>
@@ -1624,13 +1624,13 @@
         <v>16.4931</v>
       </c>
       <c r="S15" t="n">
-        <v>7.145600000000002</v>
+        <v>7.696000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>5.1133</v>
+        <v>5.664000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>2.032299999999999</v>
+        <v>2.0322</v>
       </c>
       <c r="V15" t="n">
         <v>3.4477</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0157</v>
+        <v>1.9249</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2072</v>
+        <v>1.5919</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1916</v>
+        <v>0.333</v>
       </c>
       <c r="G16" t="n">
         <v>-0.2424</v>
@@ -1702,13 +1702,13 @@
         <v>1.4661</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.9356</v>
+        <v>-1.0264</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2036</v>
+        <v>0.181</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.732</v>
+        <v>-1.2074</v>
       </c>
       <c r="V16" t="n">
         <v>1.9109</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. CARRION BALLESTER</t>
+          <t>R. MEDINA LERMA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4588</v>
+        <v>-1.0562</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9783</v>
+        <v>0.8361</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5194</v>
+        <v>-1.8923</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.5805</v>
+        <v>-0.1208</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.4329</v>
+        <v>0.8956</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8525</v>
+        <v>-1.0164</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.3587</v>
+        <v>1.8715</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.0255</v>
+        <v>1.8298</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6667999999999999</v>
+        <v>0.0417</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2217</v>
+        <v>-1.9923</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.4074</v>
+        <v>-0.9342</v>
       </c>
       <c r="O18" t="n">
-        <v>1.1857</v>
+        <v>-1.0581</v>
       </c>
       <c r="P18" t="n">
         <v>-0.1833</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0995</v>
+        <v>-0.9163</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9163</v>
+        <v>0.733</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2671</v>
+        <v>-0.7417</v>
       </c>
       <c r="T18" t="n">
-        <v>2.5257</v>
+        <v>-0.7526</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.2585</v>
+        <v>0.0109</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9554</v>
+        <v>-0.0104</v>
       </c>
       <c r="W18" t="n">
-        <v>1.9109</v>
+        <v>0.6335</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.9554</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. MEDINA LERMA</t>
+          <t>A. CARRION BALLESTER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8376</v>
+        <v>-1.0971</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8361</v>
+        <v>0.3436</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6736</v>
+        <v>-1.4408</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1208</v>
+        <v>-1.5805</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8956</v>
+        <v>-3.4329</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0164</v>
+        <v>1.8525</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8715</v>
+        <v>-1.3587</v>
       </c>
       <c r="K19" t="n">
-        <v>1.8298</v>
+        <v>-2.0255</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0417</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.9923</v>
+        <v>-0.2217</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9342</v>
+        <v>-1.4074</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0581</v>
+        <v>1.1857</v>
       </c>
       <c r="P19" t="n">
         <v>-0.1833</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9163</v>
+        <v>-1.0995</v>
       </c>
       <c r="R19" t="n">
-        <v>0.733</v>
+        <v>0.9163</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5231</v>
+        <v>-0.2888</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7526</v>
+        <v>0.891</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2295</v>
+        <v>-1.1799</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.0104</v>
+        <v>0.9554</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6335</v>
+        <v>1.9109</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6439</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. SOLBES SORIANO</t>
+          <t>M. CISNEROS RUIZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3786</v>
+        <v>-1.3314</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2371</v>
+        <v>-0.0914</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1415</v>
+        <v>-1.2399</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5981</v>
+        <v>-0.8090000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3959</v>
+        <v>1.3291</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7979000000000001</v>
+        <v>-2.1381</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3367</v>
+        <v>0.156</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1793</v>
+        <v>2.0374</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.516</v>
+        <v>-1.8814</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2614</v>
+        <v>-0.965</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.5753</v>
+        <v>-0.7083</v>
       </c>
       <c r="O20" t="n">
-        <v>1.3139</v>
+        <v>-0.2567</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.5498</v>
+        <v>0.5498</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.0158</v>
+        <v>-0.1833</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4661</v>
+        <v>0.733</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4027</v>
+        <v>-0.7606000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>1.1154</v>
+        <v>-0.3861</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7127</v>
+        <v>-0.3744</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6335</v>
+        <v>-0.3115</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X20" t="n">
         <v>-0.6335</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. CISNEROS RUIZ</t>
+          <t>A. SOLBES SORIANO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8646</v>
+        <v>-1.8273</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4761</v>
+        <v>-1.814</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3886</v>
+        <v>-0.0133</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8090000000000001</v>
+        <v>-0.5981</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3291</v>
+        <v>-1.3959</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.1381</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>0.156</v>
+        <v>-0.3367</v>
       </c>
       <c r="K21" t="n">
-        <v>2.0374</v>
+        <v>0.1793</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.8814</v>
+        <v>-0.516</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.965</v>
+        <v>-0.2614</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7083</v>
+        <v>-1.5753</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2567</v>
+        <v>1.3139</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5498</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.1833</v>
+        <v>-2.0158</v>
       </c>
       <c r="R21" t="n">
-        <v>0.733</v>
+        <v>1.4661</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2938</v>
+        <v>-0.046</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7707000000000001</v>
+        <v>0.5385</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5231</v>
+        <v>-0.5845</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3115</v>
+        <v>-0.6335</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>-0.6335</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. CARRION BALLESTER</t>
+          <t>J. CARPIO MANEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8779</v>
+        <v>-2.722</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.6304</v>
+        <v>-0.1998</v>
       </c>
       <c r="F22" t="n">
-        <v>1.7525</v>
+        <v>-2.5222</v>
       </c>
       <c r="G22" t="n">
-        <v>2.2539</v>
+        <v>-0.2399</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8018999999999999</v>
+        <v>0.1895</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4519</v>
+        <v>-0.4295</v>
       </c>
       <c r="J22" t="n">
-        <v>1.0696</v>
+        <v>0.5159</v>
       </c>
       <c r="K22" t="n">
-        <v>1.0279</v>
+        <v>0.4644</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0417</v>
+        <v>0.0515</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1843</v>
+        <v>-0.7558</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2259</v>
+        <v>-0.2748</v>
       </c>
       <c r="O22" t="n">
-        <v>1.4103</v>
+        <v>-0.481</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.6651</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.5814</v>
+        <v>-0.9163</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9163</v>
+        <v>0.3665</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.21</v>
+        <v>-0.0319</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4955</v>
+        <v>0.2006</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2854</v>
+        <v>-0.2325</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2566</v>
+        <v>-1.9005</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6231</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6335</v>
+        <v>-1.9005</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. CARPIO MANEZ</t>
+          <t>R. CARRION BALLESTER</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9332</v>
+        <v>-2.8094</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5844</v>
+        <v>-4.4381</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.3488</v>
+        <v>1.6287</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2399</v>
+        <v>2.2539</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1895</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4295</v>
+        <v>1.4519</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5159</v>
+        <v>1.0696</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4644</v>
+        <v>1.0279</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0515</v>
+        <v>0.0417</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7558</v>
+        <v>1.1843</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2748</v>
+        <v>-0.2259</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.481</v>
+        <v>1.4103</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.5498</v>
+        <v>-3.6651</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9163</v>
+        <v>-4.5814</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3665</v>
+        <v>0.9163</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2431</v>
+        <v>-0.1416</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.184</v>
+        <v>-0.3032</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0591</v>
+        <v>0.1616</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.9005</v>
+        <v>-1.2566</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.6231</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.9005</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6801</v>
+        <v>-4.6292</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.2634</v>
+        <v>-4.1673</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4167</v>
+        <v>-0.4619</v>
       </c>
       <c r="G24" t="n">
         <v>-3.7221</v>
@@ -2326,13 +2326,13 @@
         <v>1.4661</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5915</v>
+        <v>-0.5405</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.046</v>
+        <v>-0.9498</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4545</v>
+        <v>0.4093</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.1872</v>
+        <v>-4.7457</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.5794</v>
+        <v>-3.2909</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.6078</v>
+        <v>-1.4548</v>
       </c>
       <c r="G25" t="n">
         <v>-4.4707</v>
@@ -2404,13 +2404,13 @@
         <v>0.9163</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7165</v>
+        <v>-0.2751</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6976</v>
+        <v>-0.4091</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0189</v>
+        <v>0.134</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.4169</v>
+        <v>-4.8224</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.9873</v>
+        <v>-0.6988</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.4296</v>
+        <v>-4.1236</v>
       </c>
       <c r="G26" t="n">
         <v>-0.8172</v>
@@ -2482,13 +2482,13 @@
         <v>0.5498</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.7988</v>
+        <v>-1.2044</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.3673</v>
+        <v>-0.0788</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.4315</v>
+        <v>-1.1256</v>
       </c>
       <c r="V26" t="n">
         <v>-3.1674</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-6.173</v>
+        <v>-5.4765</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.184</v>
+        <v>-3.9917</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.989</v>
+        <v>-1.4849</v>
       </c>
       <c r="G27" t="n">
         <v>-3.4368</v>
@@ -2560,13 +2560,13 @@
         <v>1.4661</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.503</v>
+        <v>-0.8066</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.1561</v>
+        <v>-0.9638</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.3469</v>
+        <v>0.1572</v>
       </c>
       <c r="V27" t="n">
         <v>0.9658</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-29.2495</v>
+        <v>-27.9672</v>
       </c>
       <c r="E28" t="n">
-        <v>-15.2954</v>
+        <v>-15.2953</v>
       </c>
       <c r="F28" t="n">
-        <v>-13.9541</v>
+        <v>-12.672</v>
       </c>
       <c r="G28" t="n">
         <v>-13.1585</v>
@@ -2638,13 +2638,13 @@
         <v>10.9956</v>
       </c>
       <c r="S28" t="n">
-        <v>-7.1456</v>
+        <v>-5.8636</v>
       </c>
       <c r="T28" t="n">
         <v>-2.0323</v>
       </c>
       <c r="U28" t="n">
-        <v>-5.1133</v>
+        <v>-3.8313</v>
       </c>
       <c r="V28" t="n">
         <v>-3.447800000000001</v>
